--- a/3자결함_분석용.xlsx
+++ b/3자결함_분석용.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\1. file trans\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2. 사업관리\TEST 품질 강화\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E6693B-6681-4019-881C-DB2ACC8B078B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{549CCB7A-5EB9-476E-8639-04C63CBE0108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{88F2D18C-2547-4E62-B99B-7D00429EFFA8}"/>
   </bookViews>
@@ -26,8 +26,6 @@
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">Sheet2!$G$3:$G$9</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">Sheet2!$H$3:$H$9</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet2!$G$3:$G$9</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet2!$H$3:$H$9</definedName>
     <definedName name="ALL">[1]Itr2_2_결함_pivot!$L$28:$W$43</definedName>
     <definedName name="C_LL">[1]Itr2_2_결함_pivot!$L$74:$T$89</definedName>
     <definedName name="DEAL">[1]Itr2_2_결함_pivot!$Z$27:$AB$42</definedName>
@@ -40,8 +38,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="17" r:id="rId8"/>
-    <pivotCache cacheId="32" r:id="rId9"/>
+    <pivotCache cacheId="391" r:id="rId8"/>
+    <pivotCache cacheId="392" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2891,6 +2889,7 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="KoPub돋움체 Medium"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
@@ -3299,9 +3298,6 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3314,22 +3310,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -3343,6 +3327,21 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3667,7 +3666,7 @@
         <c:idx val="4"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent3"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -3967,6 +3966,16 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000006-5272-459F-8A50-DDC3E357D894}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
@@ -4394,6 +4403,104 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -4427,6 +4534,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-D104-4175-B08C-25CF4E29089A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -4442,6 +4554,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-D104-4175-B08C-25CF4E29089A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -4457,6 +4574,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-D104-4175-B08C-25CF4E29089A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -4472,6 +4594,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-D104-4175-B08C-25CF4E29089A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -4487,6 +4614,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-D104-4175-B08C-25CF4E29089A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -4502,6 +4634,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-D104-4175-B08C-25CF4E29089A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -4519,6 +4656,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-D104-4175-B08C-25CF4E29089A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -19728,7 +19870,217 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6A15CCBF-7EB9-4876-AB2C-D09C13DB4D65}" name="피벗 테이블2" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="24">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{65CD43AC-9179-4270-9F3D-80E310044A27}" name="피벗 테이블1" cacheId="391" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="A3:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="19">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="17">
+        <item x="0"/>
+        <item x="11"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="8">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="7">
+        <item x="5"/>
+        <item h="1" x="2"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="12"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="16" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="개수 : 결함ID" fld="4" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="8">
+    <chartFormat chart="8" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6A15CCBF-7EB9-4876-AB2C-D09C13DB4D65}" name="피벗 테이블2" cacheId="391" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="24">
   <location ref="A28:E30" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
@@ -19903,134 +20255,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{65CD43AC-9179-4270-9F3D-80E310044A27}" name="피벗 테이블1" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="A3:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="19">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="17">
-        <item x="0"/>
-        <item x="11"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="12"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="8">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="7">
-        <item x="5"/>
-        <item h="1" x="2"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="12"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="16" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="개수 : 결함ID" fld="4" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="8" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B811A91D-4D09-46BB-BD84-ED209517C8A7}" name="피벗 테이블7" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B811A91D-4D09-46BB-BD84-ED209517C8A7}" name="피벗 테이블7" cacheId="391" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C20" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
@@ -20066,7 +20292,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{291EC761-0D13-474D-86AC-00968DFE106D}" name="피벗 테이블8" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{291EC761-0D13-474D-86AC-00968DFE106D}" name="피벗 테이블8" cacheId="391" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C20" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
@@ -20102,7 +20328,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0886CCC4-AE31-4CFA-AAF1-E4E50D2BF6AD}" name="피벗 테이블9" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0886CCC4-AE31-4CFA-AAF1-E4E50D2BF6AD}" name="피벗 테이블9" cacheId="392" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:K21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="20">
     <pivotField showAll="0"/>
@@ -37994,802 +38220,802 @@
       </c>
     </row>
     <row r="24" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="N24" s="40" t="s">
+      <c r="N24" s="43" t="s">
         <v>842</v>
       </c>
-      <c r="O24" s="41"/>
+      <c r="O24" s="44"/>
       <c r="P24" s="31" t="s">
         <v>837</v>
       </c>
-      <c r="Q24" s="45" t="s">
+      <c r="Q24" s="40" t="s">
         <v>808</v>
       </c>
-      <c r="R24" s="45" t="s">
+      <c r="R24" s="40" t="s">
         <v>809</v>
       </c>
-      <c r="S24" s="45" t="s">
+      <c r="S24" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="T24" s="45" t="s">
+      <c r="T24" s="40" t="s">
         <v>810</v>
       </c>
-      <c r="U24" s="45" t="s">
+      <c r="U24" s="40" t="s">
         <v>811</v>
       </c>
-      <c r="V24" s="45" t="s">
+      <c r="V24" s="40" t="s">
         <v>813</v>
       </c>
-      <c r="W24" s="45" t="s">
+      <c r="W24" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="X24" s="45" t="s">
+      <c r="X24" s="40" t="s">
         <v>814</v>
       </c>
-      <c r="Y24" s="46" t="s">
+      <c r="Y24" s="41" t="s">
         <v>841</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="N25" s="32" t="s">
+      <c r="N25" s="45" t="s">
         <v>838</v>
       </c>
-      <c r="O25" s="33" t="s">
+      <c r="O25" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="P25" s="34">
+      <c r="P25" s="33">
         <v>22</v>
       </c>
-      <c r="Q25" s="35">
+      <c r="Q25" s="34">
+        <f t="shared" ref="Q25:Q40" si="0">VLOOKUP(O25,tag,9,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="R25" s="34">
+        <f t="shared" ref="R25:R40" si="1">VLOOKUP(O25,tag,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="S25" s="35">
+        <f t="shared" ref="S25:S40" si="2">VLOOKUP(O25,tag,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="T25" s="34">
+        <f t="shared" ref="T25:T40" si="3">VLOOKUP(O25,tag,10,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="U25" s="34">
+        <f t="shared" ref="U25:U40" si="4">VLOOKUP(O25,tag,3,FALSE)+VLOOKUP(O25,tag,4,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="V25" s="34">
+        <f t="shared" ref="V25:V40" si="5">VLOOKUP(O25,tag,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="W25" s="34">
+        <f t="shared" ref="W25:W40" si="6">VLOOKUP(O25,tag,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="X25" s="35">
+        <f t="shared" ref="X25:X40" si="7">VLOOKUP(O25,tag,5,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="Y25" s="35">
+        <f>SUM(Q25:X25)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="N26" s="45"/>
+      <c r="O26" s="32" t="s">
+        <v>729</v>
+      </c>
+      <c r="P26" s="33">
+        <v>11</v>
+      </c>
+      <c r="Q26" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R26" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="35">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="T26" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="35">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="35">
+        <f t="shared" ref="Y26:Y41" si="8">SUM(Q26:X26)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="N27" s="45"/>
+      <c r="O27" s="32" t="s">
+        <v>429</v>
+      </c>
+      <c r="P27" s="33">
+        <v>42</v>
+      </c>
+      <c r="Q27" s="34">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R27" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="35">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="T27" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="35">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="Y27" s="35">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="N28" s="45"/>
+      <c r="O28" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="P28" s="33">
+        <v>55</v>
+      </c>
+      <c r="Q28" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R28" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="35">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="T28" s="34">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="U28" s="34">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="V28" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="35">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="Y28" s="35">
+        <f t="shared" si="8"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="N29" s="45"/>
+      <c r="O29" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="P29" s="33">
+        <v>51</v>
+      </c>
+      <c r="Q29" s="34">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="R29" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="35">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="T29" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="34">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="W29" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X29" s="35">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="Y29" s="35">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N30" s="45" t="s">
+        <v>839</v>
+      </c>
+      <c r="O30" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="P30" s="33">
+        <v>78</v>
+      </c>
+      <c r="Q30" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R30" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="35">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="T30" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="34">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="V30" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X30" s="35">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="35">
+        <f t="shared" si="8"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="N31" s="45"/>
+      <c r="O31" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="P31" s="33">
+        <v>51</v>
+      </c>
+      <c r="Q31" s="34">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="R31" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="35">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="T31" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X31" s="35">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="Y31" s="35">
+        <f t="shared" si="8"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="N32" s="45"/>
+      <c r="O32" s="32" t="s">
+        <v>465</v>
+      </c>
+      <c r="P32" s="33">
+        <v>18</v>
+      </c>
+      <c r="Q32" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R32" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="35">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="T32" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="35">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="35">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="14:25" x14ac:dyDescent="0.3">
+      <c r="N33" s="45"/>
+      <c r="O33" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="P33" s="33">
+        <v>90</v>
+      </c>
+      <c r="Q33" s="34">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="R33" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="35">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="T33" s="34">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="U33" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="35">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="Y33" s="35">
+        <f t="shared" si="8"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="14:25" x14ac:dyDescent="0.3">
+      <c r="N34" s="45"/>
+      <c r="O34" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="P34" s="33">
+        <v>65</v>
+      </c>
+      <c r="Q34" s="34">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="R34" s="34">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S34" s="35">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="T34" s="34">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="U34" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="34">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="X34" s="35">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="Y34" s="35">
+        <f t="shared" si="8"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="14:25" x14ac:dyDescent="0.3">
+      <c r="N35" s="45"/>
+      <c r="O35" s="32" t="s">
+        <v>648</v>
+      </c>
+      <c r="P35" s="33">
+        <v>57</v>
+      </c>
+      <c r="Q35" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R35" s="34">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S35" s="35">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="T35" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W35" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X35" s="35">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="Y35" s="35">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="14:25" x14ac:dyDescent="0.3">
+      <c r="N36" s="46" t="s">
+        <v>840</v>
+      </c>
+      <c r="O36" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="P36" s="33">
+        <v>10</v>
+      </c>
+      <c r="Q36" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R36" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="35">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="T36" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="35">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="Y36" s="35">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="14:25" x14ac:dyDescent="0.3">
+      <c r="N37" s="46"/>
+      <c r="O37" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="P37" s="33">
+        <v>19</v>
+      </c>
+      <c r="Q37" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R37" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="35">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="T37" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="35">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="35">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="14:25" x14ac:dyDescent="0.3">
+      <c r="N38" s="46"/>
+      <c r="O38" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="P38" s="33">
+        <v>41</v>
+      </c>
+      <c r="Q38" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R38" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S38" s="35">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="T38" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V38" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W38" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X38" s="35">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="Y38" s="35">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="14:25" x14ac:dyDescent="0.3">
+      <c r="N39" s="46"/>
+      <c r="O39" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="P39" s="33">
+        <v>19</v>
+      </c>
+      <c r="Q39" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R39" s="34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="35">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="T39" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V39" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="34">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="X39" s="35">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="35">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="14:25" x14ac:dyDescent="0.3">
+      <c r="N40" s="46"/>
+      <c r="O40" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="P40" s="37">
+        <v>10</v>
+      </c>
+      <c r="Q40" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R40" s="34">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S40" s="35">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="T40" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="35">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="Y40" s="35">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="14:25" x14ac:dyDescent="0.3">
+      <c r="N41" s="46"/>
+      <c r="O41" s="32" t="s">
+        <v>836</v>
+      </c>
+      <c r="P41" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="34">
+        <v>0</v>
+      </c>
+      <c r="R41" s="34">
+        <v>0</v>
+      </c>
+      <c r="S41" s="35">
+        <v>0</v>
+      </c>
+      <c r="T41" s="34">
+        <v>0</v>
+      </c>
+      <c r="U41" s="34">
         <f>VLOOKUP(O25,tag,9,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="R25" s="35">
-        <f>VLOOKUP(O25,tag,8,FALSE)</f>
+      <c r="V41" s="35">
         <v>0</v>
       </c>
-      <c r="S25" s="36">
-        <f>VLOOKUP(O25,tag,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="T25" s="35">
-        <f>VLOOKUP(O25,tag,10,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="U25" s="35">
-        <f>VLOOKUP(O25,tag,3,FALSE)+VLOOKUP(O25,tag,4,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="V25" s="35">
-        <f>VLOOKUP(O25,tag,6,FALSE)</f>
+      <c r="W41" s="35">
         <v>0</v>
       </c>
-      <c r="W25" s="35">
-        <f>VLOOKUP(O25,tag,7,FALSE)</f>
+      <c r="X41" s="35">
         <v>0</v>
       </c>
-      <c r="X25" s="36">
-        <f>VLOOKUP(O25,tag,5,FALSE)</f>
-        <v>7</v>
-      </c>
-      <c r="Y25" s="36">
-        <f>SUM(Q25:X25)</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="N26" s="32"/>
-      <c r="O26" s="33" t="s">
-        <v>729</v>
-      </c>
-      <c r="P26" s="34">
-        <v>11</v>
-      </c>
-      <c r="Q26" s="35">
-        <f>VLOOKUP(O26,tag,9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="R26" s="35">
-        <f>VLOOKUP(O26,tag,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="S26" s="36">
-        <f>VLOOKUP(O26,tag,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="T26" s="35">
-        <f>VLOOKUP(O26,tag,10,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="U26" s="35">
-        <f>VLOOKUP(O26,tag,3,FALSE)+VLOOKUP(O26,tag,4,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="V26" s="35">
-        <f>VLOOKUP(O26,tag,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="W26" s="35">
-        <f>VLOOKUP(O26,tag,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="X26" s="36">
-        <f>VLOOKUP(O26,tag,5,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="36">
-        <f t="shared" ref="Y26:Y41" si="0">SUM(Q26:X26)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="N27" s="32"/>
-      <c r="O27" s="33" t="s">
-        <v>429</v>
-      </c>
-      <c r="P27" s="34">
-        <v>42</v>
-      </c>
-      <c r="Q27" s="35">
-        <f>VLOOKUP(O27,tag,9,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="R27" s="35">
-        <f>VLOOKUP(O27,tag,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="S27" s="36">
-        <f>VLOOKUP(O27,tag,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="T27" s="35">
-        <f>VLOOKUP(O27,tag,10,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="U27" s="35">
-        <f>VLOOKUP(O27,tag,3,FALSE)+VLOOKUP(O27,tag,4,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="V27" s="35">
-        <f>VLOOKUP(O27,tag,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="W27" s="35">
-        <f>VLOOKUP(O27,tag,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="X27" s="36">
-        <f>VLOOKUP(O27,tag,5,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="Y27" s="36">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="N28" s="32"/>
-      <c r="O28" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="P28" s="34">
-        <v>55</v>
-      </c>
-      <c r="Q28" s="35">
-        <f>VLOOKUP(O28,tag,9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="R28" s="35">
-        <f>VLOOKUP(O28,tag,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="S28" s="36">
-        <f>VLOOKUP(O28,tag,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="T28" s="35">
-        <f>VLOOKUP(O28,tag,10,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="U28" s="35">
-        <f>VLOOKUP(O28,tag,3,FALSE)+VLOOKUP(O28,tag,4,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="V28" s="35">
-        <f>VLOOKUP(O28,tag,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="W28" s="35">
-        <f>VLOOKUP(O28,tag,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="X28" s="36">
-        <f>VLOOKUP(O28,tag,5,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="Y28" s="36">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="N29" s="32"/>
-      <c r="O29" s="33" t="s">
-        <v>50</v>
-      </c>
-      <c r="P29" s="34">
-        <v>51</v>
-      </c>
-      <c r="Q29" s="35">
-        <f>VLOOKUP(O29,tag,9,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="R29" s="35">
-        <f>VLOOKUP(O29,tag,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="S29" s="36">
-        <f>VLOOKUP(O29,tag,2,FALSE)</f>
-        <v>9</v>
-      </c>
-      <c r="T29" s="35">
-        <f>VLOOKUP(O29,tag,10,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="U29" s="35">
-        <f>VLOOKUP(O29,tag,3,FALSE)+VLOOKUP(O29,tag,4,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="V29" s="35">
-        <f>VLOOKUP(O29,tag,6,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="W29" s="35">
-        <f>VLOOKUP(O29,tag,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="X29" s="36">
-        <f>VLOOKUP(O29,tag,5,FALSE)</f>
-        <v>9</v>
-      </c>
-      <c r="Y29" s="36">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="N30" s="32" t="s">
-        <v>839</v>
-      </c>
-      <c r="O30" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="P30" s="34">
-        <v>78</v>
-      </c>
-      <c r="Q30" s="35">
-        <f>VLOOKUP(O30,tag,9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="R30" s="35">
-        <f>VLOOKUP(O30,tag,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="S30" s="36">
-        <f>VLOOKUP(O30,tag,2,FALSE)</f>
-        <v>16</v>
-      </c>
-      <c r="T30" s="35">
-        <f>VLOOKUP(O30,tag,10,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="U30" s="35">
-        <f>VLOOKUP(O30,tag,3,FALSE)+VLOOKUP(O30,tag,4,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="V30" s="35">
-        <f>VLOOKUP(O30,tag,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="W30" s="35">
-        <f>VLOOKUP(O30,tag,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="X30" s="36">
-        <f>VLOOKUP(O30,tag,5,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="Y30" s="36">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="N31" s="32"/>
-      <c r="O31" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="P31" s="34">
-        <v>51</v>
-      </c>
-      <c r="Q31" s="35">
-        <f>VLOOKUP(O31,tag,9,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="R31" s="35">
-        <f>VLOOKUP(O31,tag,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="S31" s="36">
-        <f>VLOOKUP(O31,tag,2,FALSE)</f>
-        <v>16</v>
-      </c>
-      <c r="T31" s="35">
-        <f>VLOOKUP(O31,tag,10,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="U31" s="35">
-        <f>VLOOKUP(O31,tag,3,FALSE)+VLOOKUP(O31,tag,4,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="V31" s="35">
-        <f>VLOOKUP(O31,tag,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="W31" s="35">
-        <f>VLOOKUP(O31,tag,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="X31" s="36">
-        <f>VLOOKUP(O31,tag,5,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="Y31" s="36">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="N32" s="32"/>
-      <c r="O32" s="33" t="s">
-        <v>465</v>
-      </c>
-      <c r="P32" s="34">
-        <v>18</v>
-      </c>
-      <c r="Q32" s="35">
-        <f>VLOOKUP(O32,tag,9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="R32" s="35">
-        <f>VLOOKUP(O32,tag,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="S32" s="36">
-        <f>VLOOKUP(O32,tag,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="T32" s="35">
-        <f>VLOOKUP(O32,tag,10,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="U32" s="35">
-        <f>VLOOKUP(O32,tag,3,FALSE)+VLOOKUP(O32,tag,4,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="V32" s="35">
-        <f>VLOOKUP(O32,tag,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="W32" s="35">
-        <f>VLOOKUP(O32,tag,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="X32" s="36">
-        <f>VLOOKUP(O32,tag,5,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="36">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="14:25" x14ac:dyDescent="0.3">
-      <c r="N33" s="32"/>
-      <c r="O33" s="33" t="s">
-        <v>116</v>
-      </c>
-      <c r="P33" s="34">
-        <v>90</v>
-      </c>
-      <c r="Q33" s="35">
-        <f>VLOOKUP(O33,tag,9,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="R33" s="35">
-        <f>VLOOKUP(O33,tag,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="S33" s="36">
-        <f>VLOOKUP(O33,tag,2,FALSE)</f>
-        <v>8</v>
-      </c>
-      <c r="T33" s="35">
-        <f>VLOOKUP(O33,tag,10,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="U33" s="35">
-        <f>VLOOKUP(O33,tag,3,FALSE)+VLOOKUP(O33,tag,4,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="V33" s="35">
-        <f>VLOOKUP(O33,tag,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="W33" s="35">
-        <f>VLOOKUP(O33,tag,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="X33" s="36">
-        <f>VLOOKUP(O33,tag,5,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="Y33" s="36">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="14:25" x14ac:dyDescent="0.3">
-      <c r="N34" s="32"/>
-      <c r="O34" s="33" t="s">
-        <v>165</v>
-      </c>
-      <c r="P34" s="34">
-        <v>65</v>
-      </c>
-      <c r="Q34" s="35">
-        <f>VLOOKUP(O34,tag,9,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="R34" s="35">
-        <f>VLOOKUP(O34,tag,8,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="S34" s="36">
-        <f>VLOOKUP(O34,tag,2,FALSE)</f>
-        <v>8</v>
-      </c>
-      <c r="T34" s="35">
-        <f>VLOOKUP(O34,tag,10,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="U34" s="35">
-        <f>VLOOKUP(O34,tag,3,FALSE)+VLOOKUP(O34,tag,4,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="V34" s="35">
-        <f>VLOOKUP(O34,tag,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="W34" s="35">
-        <f>VLOOKUP(O34,tag,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="X34" s="36">
-        <f>VLOOKUP(O34,tag,5,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="Y34" s="36">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="14:25" x14ac:dyDescent="0.3">
-      <c r="N35" s="32"/>
-      <c r="O35" s="33" t="s">
-        <v>648</v>
-      </c>
-      <c r="P35" s="34">
-        <v>57</v>
-      </c>
-      <c r="Q35" s="35">
-        <f>VLOOKUP(O35,tag,9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="R35" s="35">
-        <f>VLOOKUP(O35,tag,8,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="S35" s="36">
-        <f>VLOOKUP(O35,tag,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="T35" s="35">
-        <f>VLOOKUP(O35,tag,10,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="U35" s="35">
-        <f>VLOOKUP(O35,tag,3,FALSE)+VLOOKUP(O35,tag,4,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="V35" s="35">
-        <f>VLOOKUP(O35,tag,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="W35" s="35">
-        <f>VLOOKUP(O35,tag,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="X35" s="36">
-        <f>VLOOKUP(O35,tag,5,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="Y35" s="36">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="14:25" x14ac:dyDescent="0.3">
-      <c r="N36" s="37" t="s">
-        <v>840</v>
-      </c>
-      <c r="O36" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="P36" s="34">
-        <v>10</v>
-      </c>
-      <c r="Q36" s="35">
-        <f>VLOOKUP(O36,tag,9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="R36" s="35">
-        <f>VLOOKUP(O36,tag,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="S36" s="36">
-        <f>VLOOKUP(O36,tag,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="T36" s="35">
-        <f>VLOOKUP(O36,tag,10,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="U36" s="35">
-        <f>VLOOKUP(O36,tag,3,FALSE)+VLOOKUP(O36,tag,4,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="V36" s="35">
-        <f>VLOOKUP(O36,tag,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="W36" s="35">
-        <f>VLOOKUP(O36,tag,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="X36" s="36">
-        <f>VLOOKUP(O36,tag,5,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="Y36" s="36">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="14:25" x14ac:dyDescent="0.3">
-      <c r="N37" s="37"/>
-      <c r="O37" s="33" t="s">
-        <v>244</v>
-      </c>
-      <c r="P37" s="34">
-        <v>19</v>
-      </c>
-      <c r="Q37" s="35">
-        <f>VLOOKUP(O37,tag,9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="R37" s="35">
-        <f>VLOOKUP(O37,tag,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="S37" s="36">
-        <f>VLOOKUP(O37,tag,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="T37" s="35">
-        <f>VLOOKUP(O37,tag,10,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="U37" s="35">
-        <f>VLOOKUP(O37,tag,3,FALSE)+VLOOKUP(O37,tag,4,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="V37" s="35">
-        <f>VLOOKUP(O37,tag,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="W37" s="35">
-        <f>VLOOKUP(O37,tag,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="X37" s="36">
-        <f>VLOOKUP(O37,tag,5,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="Y37" s="36">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="14:25" x14ac:dyDescent="0.3">
-      <c r="N38" s="37"/>
-      <c r="O38" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="P38" s="34">
-        <v>41</v>
-      </c>
-      <c r="Q38" s="35">
-        <f>VLOOKUP(O38,tag,9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="R38" s="35">
-        <f>VLOOKUP(O38,tag,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="S38" s="36">
-        <f>VLOOKUP(O38,tag,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="T38" s="35">
-        <f>VLOOKUP(O38,tag,10,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="U38" s="35">
-        <f>VLOOKUP(O38,tag,3,FALSE)+VLOOKUP(O38,tag,4,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="V38" s="35">
-        <f>VLOOKUP(O38,tag,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="W38" s="35">
-        <f>VLOOKUP(O38,tag,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="X38" s="36">
-        <f>VLOOKUP(O38,tag,5,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="Y38" s="36">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="14:25" x14ac:dyDescent="0.3">
-      <c r="N39" s="37"/>
-      <c r="O39" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="P39" s="34">
-        <v>19</v>
-      </c>
-      <c r="Q39" s="35">
-        <f>VLOOKUP(O39,tag,9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="R39" s="35">
-        <f>VLOOKUP(O39,tag,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="S39" s="36">
-        <f>VLOOKUP(O39,tag,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="T39" s="35">
-        <f>VLOOKUP(O39,tag,10,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="U39" s="35">
-        <f>VLOOKUP(O39,tag,3,FALSE)+VLOOKUP(O39,tag,4,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="V39" s="35">
-        <f>VLOOKUP(O39,tag,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="W39" s="35">
-        <f>VLOOKUP(O39,tag,7,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="X39" s="36">
-        <f>VLOOKUP(O39,tag,5,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="Y39" s="36">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="14:25" x14ac:dyDescent="0.3">
-      <c r="N40" s="37"/>
-      <c r="O40" s="38" t="s">
-        <v>198</v>
-      </c>
-      <c r="P40" s="39">
-        <v>10</v>
-      </c>
-      <c r="Q40" s="35">
-        <f>VLOOKUP(O40,tag,9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="R40" s="35">
-        <f>VLOOKUP(O40,tag,8,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="S40" s="36">
-        <f>VLOOKUP(O40,tag,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="T40" s="35">
-        <f>VLOOKUP(O40,tag,10,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="U40" s="35">
-        <f>VLOOKUP(O40,tag,3,FALSE)+VLOOKUP(O40,tag,4,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="V40" s="35">
-        <f>VLOOKUP(O40,tag,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="W40" s="35">
-        <f>VLOOKUP(O40,tag,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="X40" s="36">
-        <f>VLOOKUP(O40,tag,5,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="Y40" s="36">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="14:25" x14ac:dyDescent="0.3">
-      <c r="N41" s="37"/>
-      <c r="O41" s="33" t="s">
-        <v>836</v>
-      </c>
-      <c r="P41" s="34">
-        <v>1</v>
-      </c>
-      <c r="Q41" s="35">
-        <v>0</v>
-      </c>
-      <c r="R41" s="35">
-        <v>0</v>
-      </c>
-      <c r="S41" s="36">
-        <v>0</v>
-      </c>
-      <c r="T41" s="35">
-        <v>0</v>
-      </c>
-      <c r="U41" s="35">
-        <f>VLOOKUP(O25,tag,9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="V41" s="36">
-        <v>0</v>
-      </c>
-      <c r="W41" s="36">
-        <v>0</v>
-      </c>
-      <c r="X41" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="36">
-        <f t="shared" si="0"/>
+      <c r="Y41" s="35">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -38798,43 +39024,43 @@
         <v>841</v>
       </c>
       <c r="O42" s="42"/>
-      <c r="P42" s="43">
+      <c r="P42" s="38">
         <f>SUM(P25:P41)</f>
         <v>640</v>
       </c>
-      <c r="Q42" s="44">
+      <c r="Q42" s="39">
         <f>SUM(Q25:Q41)</f>
         <v>14</v>
       </c>
-      <c r="R42" s="44">
-        <f t="shared" ref="R42:X42" si="1">SUM(R25:R41)</f>
+      <c r="R42" s="39">
+        <f t="shared" ref="R42:X42" si="9">SUM(R25:R41)</f>
         <v>4</v>
       </c>
-      <c r="S42" s="44">
-        <f t="shared" si="1"/>
+      <c r="S42" s="39">
+        <f t="shared" si="9"/>
         <v>87</v>
       </c>
-      <c r="T42" s="44">
-        <f t="shared" si="1"/>
+      <c r="T42" s="39">
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="U42" s="44">
-        <f t="shared" si="1"/>
+      <c r="U42" s="39">
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="V42" s="44">
-        <f t="shared" si="1"/>
+      <c r="V42" s="39">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="W42" s="44">
-        <f t="shared" si="1"/>
+      <c r="W42" s="39">
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="X42" s="44">
-        <f t="shared" si="1"/>
+      <c r="X42" s="39">
+        <f t="shared" si="9"/>
         <v>39</v>
       </c>
-      <c r="Y42" s="43">
+      <c r="Y42" s="38">
         <f>SUM(Y25:Y41)</f>
         <v>161</v>
       </c>
@@ -38923,7 +39149,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="132" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>19</v>
       </c>
@@ -39171,7 +39397,7 @@
         <v>46044.670740740738</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="264" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>40</v>
       </c>
@@ -39667,7 +39893,7 @@
         <v>46042.731064814812</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="231" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>76</v>
       </c>
@@ -40163,7 +40389,7 @@
         <v>46044.574837962966</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="148.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>109</v>
       </c>
@@ -42637,7 +42863,7 @@
         <v>46048.590254629627</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="247.5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:20" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>44</v>
       </c>
@@ -42699,7 +42925,7 @@
         <v>46048.592118055552</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:20" ht="99" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>32</v>
       </c>
@@ -43247,7 +43473,7 @@
         <v>46048.552395833336</v>
       </c>
     </row>
-    <row r="72" spans="1:20" ht="363" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:20" ht="66" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>271</v>
       </c>
@@ -48709,7 +48935,7 @@
         <v>46048.600960648146</v>
       </c>
     </row>
-    <row r="161" spans="1:20" ht="115.5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:20" ht="33" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
         <v>510</v>
       </c>
@@ -48833,7 +49059,7 @@
         <v>46048.584270833337</v>
       </c>
     </row>
-    <row r="163" spans="1:20" ht="165" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:20" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
         <v>481</v>
       </c>

--- a/3자결함_분석용.xlsx
+++ b/3자결함_분석용.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2. 사업관리\TEST 품질 강화\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\1. file trans\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{549CCB7A-5EB9-476E-8639-04C63CBE0108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E6693B-6681-4019-881C-DB2ACC8B078B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{88F2D18C-2547-4E62-B99B-7D00429EFFA8}"/>
   </bookViews>
@@ -26,6 +26,8 @@
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">Sheet2!$G$3:$G$9</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">Sheet2!$H$3:$H$9</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet2!$G$3:$G$9</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet2!$H$3:$H$9</definedName>
     <definedName name="ALL">[1]Itr2_2_결함_pivot!$L$28:$W$43</definedName>
     <definedName name="C_LL">[1]Itr2_2_결함_pivot!$L$74:$T$89</definedName>
     <definedName name="DEAL">[1]Itr2_2_결함_pivot!$Z$27:$AB$42</definedName>
@@ -38,8 +40,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="391" r:id="rId8"/>
-    <pivotCache cacheId="392" r:id="rId9"/>
+    <pivotCache cacheId="17" r:id="rId8"/>
+    <pivotCache cacheId="32" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2889,7 +2891,6 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="KoPub돋움체 Medium"/>
-      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
@@ -3298,6 +3299,9 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3310,10 +3314,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -3327,21 +3343,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3666,7 +3667,7 @@
         <c:idx val="4"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent3"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -3966,16 +3967,6 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000006-5272-459F-8A50-DDC3E357D894}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
@@ -4403,104 +4394,6 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="4"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="5"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="6"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="7"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -4534,11 +4427,6 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-D104-4175-B08C-25CF4E29089A}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -4554,11 +4442,6 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-D104-4175-B08C-25CF4E29089A}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -4574,11 +4457,6 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-D104-4175-B08C-25CF4E29089A}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -4594,11 +4472,6 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-D104-4175-B08C-25CF4E29089A}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -4614,11 +4487,6 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-D104-4175-B08C-25CF4E29089A}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -4634,11 +4502,6 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-D104-4175-B08C-25CF4E29089A}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -4656,11 +4519,6 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-D104-4175-B08C-25CF4E29089A}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -19870,217 +19728,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{65CD43AC-9179-4270-9F3D-80E310044A27}" name="피벗 테이블1" cacheId="391" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="A3:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="19">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="17">
-        <item x="0"/>
-        <item x="11"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="12"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="8">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="7">
-        <item x="5"/>
-        <item h="1" x="2"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="12"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="16" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="개수 : 결함ID" fld="4" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="8">
-    <chartFormat chart="8" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="4">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6A15CCBF-7EB9-4876-AB2C-D09C13DB4D65}" name="피벗 테이블2" cacheId="391" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="24">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6A15CCBF-7EB9-4876-AB2C-D09C13DB4D65}" name="피벗 테이블2" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="24">
   <location ref="A28:E30" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
@@ -20255,8 +19903,134 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{65CD43AC-9179-4270-9F3D-80E310044A27}" name="피벗 테이블1" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="A3:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="19">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="17">
+        <item x="0"/>
+        <item x="11"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="8">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="7">
+        <item x="5"/>
+        <item h="1" x="2"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="12"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="16" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="개수 : 결함ID" fld="4" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="8" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B811A91D-4D09-46BB-BD84-ED209517C8A7}" name="피벗 테이블7" cacheId="391" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B811A91D-4D09-46BB-BD84-ED209517C8A7}" name="피벗 테이블7" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C20" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
@@ -20292,7 +20066,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{291EC761-0D13-474D-86AC-00968DFE106D}" name="피벗 테이블8" cacheId="391" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{291EC761-0D13-474D-86AC-00968DFE106D}" name="피벗 테이블8" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C20" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
@@ -20328,7 +20102,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0886CCC4-AE31-4CFA-AAF1-E4E50D2BF6AD}" name="피벗 테이블9" cacheId="392" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0886CCC4-AE31-4CFA-AAF1-E4E50D2BF6AD}" name="피벗 테이블9" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:K21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="20">
     <pivotField showAll="0"/>
@@ -38220,802 +37994,802 @@
       </c>
     </row>
     <row r="24" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="N24" s="43" t="s">
+      <c r="N24" s="40" t="s">
         <v>842</v>
       </c>
-      <c r="O24" s="44"/>
+      <c r="O24" s="41"/>
       <c r="P24" s="31" t="s">
         <v>837</v>
       </c>
-      <c r="Q24" s="40" t="s">
+      <c r="Q24" s="45" t="s">
         <v>808</v>
       </c>
-      <c r="R24" s="40" t="s">
+      <c r="R24" s="45" t="s">
         <v>809</v>
       </c>
-      <c r="S24" s="40" t="s">
+      <c r="S24" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="T24" s="40" t="s">
+      <c r="T24" s="45" t="s">
         <v>810</v>
       </c>
-      <c r="U24" s="40" t="s">
+      <c r="U24" s="45" t="s">
         <v>811</v>
       </c>
-      <c r="V24" s="40" t="s">
+      <c r="V24" s="45" t="s">
         <v>813</v>
       </c>
-      <c r="W24" s="40" t="s">
+      <c r="W24" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="X24" s="40" t="s">
+      <c r="X24" s="45" t="s">
         <v>814</v>
       </c>
-      <c r="Y24" s="41" t="s">
+      <c r="Y24" s="46" t="s">
         <v>841</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="N25" s="45" t="s">
+      <c r="N25" s="32" t="s">
         <v>838</v>
       </c>
-      <c r="O25" s="32" t="s">
+      <c r="O25" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="P25" s="33">
+      <c r="P25" s="34">
         <v>22</v>
       </c>
-      <c r="Q25" s="34">
-        <f t="shared" ref="Q25:Q40" si="0">VLOOKUP(O25,tag,9,FALSE)</f>
+      <c r="Q25" s="35">
+        <f>VLOOKUP(O25,tag,9,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="R25" s="34">
-        <f t="shared" ref="R25:R40" si="1">VLOOKUP(O25,tag,8,FALSE)</f>
+      <c r="R25" s="35">
+        <f>VLOOKUP(O25,tag,8,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="S25" s="35">
-        <f t="shared" ref="S25:S40" si="2">VLOOKUP(O25,tag,2,FALSE)</f>
+      <c r="S25" s="36">
+        <f>VLOOKUP(O25,tag,2,FALSE)</f>
         <v>5</v>
       </c>
-      <c r="T25" s="34">
-        <f t="shared" ref="T25:T40" si="3">VLOOKUP(O25,tag,10,FALSE)</f>
+      <c r="T25" s="35">
+        <f>VLOOKUP(O25,tag,10,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="U25" s="34">
-        <f t="shared" ref="U25:U40" si="4">VLOOKUP(O25,tag,3,FALSE)+VLOOKUP(O25,tag,4,FALSE)</f>
+      <c r="U25" s="35">
+        <f>VLOOKUP(O25,tag,3,FALSE)+VLOOKUP(O25,tag,4,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="V25" s="34">
-        <f t="shared" ref="V25:V40" si="5">VLOOKUP(O25,tag,6,FALSE)</f>
+      <c r="V25" s="35">
+        <f>VLOOKUP(O25,tag,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="W25" s="34">
-        <f t="shared" ref="W25:W40" si="6">VLOOKUP(O25,tag,7,FALSE)</f>
+      <c r="W25" s="35">
+        <f>VLOOKUP(O25,tag,7,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="X25" s="35">
-        <f t="shared" ref="X25:X40" si="7">VLOOKUP(O25,tag,5,FALSE)</f>
+      <c r="X25" s="36">
+        <f>VLOOKUP(O25,tag,5,FALSE)</f>
         <v>7</v>
       </c>
-      <c r="Y25" s="35">
+      <c r="Y25" s="36">
         <f>SUM(Q25:X25)</f>
         <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="N26" s="45"/>
-      <c r="O26" s="32" t="s">
+      <c r="N26" s="32"/>
+      <c r="O26" s="33" t="s">
         <v>729</v>
       </c>
-      <c r="P26" s="33">
+      <c r="P26" s="34">
         <v>11</v>
       </c>
-      <c r="Q26" s="34">
+      <c r="Q26" s="35">
+        <f>VLOOKUP(O26,tag,9,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="R26" s="35">
+        <f>VLOOKUP(O26,tag,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="S26" s="36">
+        <f>VLOOKUP(O26,tag,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="T26" s="35">
+        <f>VLOOKUP(O26,tag,10,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="U26" s="35">
+        <f>VLOOKUP(O26,tag,3,FALSE)+VLOOKUP(O26,tag,4,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="V26" s="35">
+        <f>VLOOKUP(O26,tag,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="W26" s="35">
+        <f>VLOOKUP(O26,tag,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="X26" s="36">
+        <f>VLOOKUP(O26,tag,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="36">
+        <f t="shared" ref="Y26:Y41" si="0">SUM(Q26:X26)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="N27" s="32"/>
+      <c r="O27" s="33" t="s">
+        <v>429</v>
+      </c>
+      <c r="P27" s="34">
+        <v>42</v>
+      </c>
+      <c r="Q27" s="35">
+        <f>VLOOKUP(O27,tag,9,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="R27" s="35">
+        <f>VLOOKUP(O27,tag,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="S27" s="36">
+        <f>VLOOKUP(O27,tag,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="T27" s="35">
+        <f>VLOOKUP(O27,tag,10,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="U27" s="35">
+        <f>VLOOKUP(O27,tag,3,FALSE)+VLOOKUP(O27,tag,4,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="V27" s="35">
+        <f>VLOOKUP(O27,tag,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="W27" s="35">
+        <f>VLOOKUP(O27,tag,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="X27" s="36">
+        <f>VLOOKUP(O27,tag,5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="Y27" s="36">
         <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="N28" s="32"/>
+      <c r="O28" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="P28" s="34">
+        <v>55</v>
+      </c>
+      <c r="Q28" s="35">
+        <f>VLOOKUP(O28,tag,9,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="R26" s="34">
-        <f t="shared" si="1"/>
+      <c r="R28" s="35">
+        <f>VLOOKUP(O28,tag,8,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="S26" s="35">
-        <f t="shared" si="2"/>
+      <c r="S28" s="36">
+        <f>VLOOKUP(O28,tag,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="T28" s="35">
+        <f>VLOOKUP(O28,tag,10,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="U28" s="35">
+        <f>VLOOKUP(O28,tag,3,FALSE)+VLOOKUP(O28,tag,4,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="V28" s="35">
+        <f>VLOOKUP(O28,tag,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="W28" s="35">
+        <f>VLOOKUP(O28,tag,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="X28" s="36">
+        <f>VLOOKUP(O28,tag,5,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="T26" s="34">
-        <f t="shared" si="3"/>
+      <c r="Y28" s="36">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="N29" s="32"/>
+      <c r="O29" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="P29" s="34">
+        <v>51</v>
+      </c>
+      <c r="Q29" s="35">
+        <f>VLOOKUP(O29,tag,9,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="R29" s="35">
+        <f>VLOOKUP(O29,tag,8,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="U26" s="34">
-        <f t="shared" si="4"/>
+      <c r="S29" s="36">
+        <f>VLOOKUP(O29,tag,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="T29" s="35">
+        <f>VLOOKUP(O29,tag,10,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="V26" s="34">
-        <f t="shared" si="5"/>
+      <c r="U29" s="35">
+        <f>VLOOKUP(O29,tag,3,FALSE)+VLOOKUP(O29,tag,4,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="W26" s="34">
-        <f t="shared" si="6"/>
+      <c r="V29" s="35">
+        <f>VLOOKUP(O29,tag,6,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="W29" s="35">
+        <f>VLOOKUP(O29,tag,7,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="X26" s="35">
-        <f t="shared" si="7"/>
+      <c r="X29" s="36">
+        <f>VLOOKUP(O29,tag,5,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="Y29" s="36">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N30" s="32" t="s">
+        <v>839</v>
+      </c>
+      <c r="O30" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="P30" s="34">
+        <v>78</v>
+      </c>
+      <c r="Q30" s="35">
+        <f>VLOOKUP(O30,tag,9,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="Y26" s="35">
-        <f t="shared" ref="Y26:Y41" si="8">SUM(Q26:X26)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="N27" s="45"/>
-      <c r="O27" s="32" t="s">
-        <v>429</v>
-      </c>
-      <c r="P27" s="33">
-        <v>42</v>
-      </c>
-      <c r="Q27" s="34">
+      <c r="R30" s="35">
+        <f>VLOOKUP(O30,tag,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="S30" s="36">
+        <f>VLOOKUP(O30,tag,2,FALSE)</f>
+        <v>16</v>
+      </c>
+      <c r="T30" s="35">
+        <f>VLOOKUP(O30,tag,10,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="U30" s="35">
+        <f>VLOOKUP(O30,tag,3,FALSE)+VLOOKUP(O30,tag,4,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="V30" s="35">
+        <f>VLOOKUP(O30,tag,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="W30" s="35">
+        <f>VLOOKUP(O30,tag,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="X30" s="36">
+        <f>VLOOKUP(O30,tag,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="36">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="N31" s="32"/>
+      <c r="O31" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="P31" s="34">
+        <v>51</v>
+      </c>
+      <c r="Q31" s="35">
+        <f>VLOOKUP(O31,tag,9,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="R31" s="35">
+        <f>VLOOKUP(O31,tag,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="S31" s="36">
+        <f>VLOOKUP(O31,tag,2,FALSE)</f>
+        <v>16</v>
+      </c>
+      <c r="T31" s="35">
+        <f>VLOOKUP(O31,tag,10,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="U31" s="35">
+        <f>VLOOKUP(O31,tag,3,FALSE)+VLOOKUP(O31,tag,4,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="V31" s="35">
+        <f>VLOOKUP(O31,tag,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="W31" s="35">
+        <f>VLOOKUP(O31,tag,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="X31" s="36">
+        <f>VLOOKUP(O31,tag,5,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="Y31" s="36">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="N32" s="32"/>
+      <c r="O32" s="33" t="s">
+        <v>465</v>
+      </c>
+      <c r="P32" s="34">
+        <v>18</v>
+      </c>
+      <c r="Q32" s="35">
+        <f>VLOOKUP(O32,tag,9,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="R32" s="35">
+        <f>VLOOKUP(O32,tag,8,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="S32" s="36">
+        <f>VLOOKUP(O32,tag,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="T32" s="35">
+        <f>VLOOKUP(O32,tag,10,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="U32" s="35">
+        <f>VLOOKUP(O32,tag,3,FALSE)+VLOOKUP(O32,tag,4,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="V32" s="35">
+        <f>VLOOKUP(O32,tag,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="W32" s="35">
+        <f>VLOOKUP(O32,tag,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="X32" s="36">
+        <f>VLOOKUP(O32,tag,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="36">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="R27" s="34">
-        <f t="shared" si="1"/>
+    </row>
+    <row r="33" spans="14:25" x14ac:dyDescent="0.3">
+      <c r="N33" s="32"/>
+      <c r="O33" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="P33" s="34">
+        <v>90</v>
+      </c>
+      <c r="Q33" s="35">
+        <f>VLOOKUP(O33,tag,9,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="R33" s="35">
+        <f>VLOOKUP(O33,tag,8,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="S27" s="35">
-        <f t="shared" si="2"/>
+      <c r="S33" s="36">
+        <f>VLOOKUP(O33,tag,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="T33" s="35">
+        <f>VLOOKUP(O33,tag,10,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="U33" s="35">
+        <f>VLOOKUP(O33,tag,3,FALSE)+VLOOKUP(O33,tag,4,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="V33" s="35">
+        <f>VLOOKUP(O33,tag,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="W33" s="35">
+        <f>VLOOKUP(O33,tag,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="X33" s="36">
+        <f>VLOOKUP(O33,tag,5,FALSE)</f>
         <v>5</v>
       </c>
-      <c r="T27" s="34">
-        <f t="shared" si="3"/>
+      <c r="Y33" s="36">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="14:25" x14ac:dyDescent="0.3">
+      <c r="N34" s="32"/>
+      <c r="O34" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="P34" s="34">
+        <v>65</v>
+      </c>
+      <c r="Q34" s="35">
+        <f>VLOOKUP(O34,tag,9,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="R34" s="35">
+        <f>VLOOKUP(O34,tag,8,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="S34" s="36">
+        <f>VLOOKUP(O34,tag,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="T34" s="35">
+        <f>VLOOKUP(O34,tag,10,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="U34" s="35">
+        <f>VLOOKUP(O34,tag,3,FALSE)+VLOOKUP(O34,tag,4,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="U27" s="34">
-        <f t="shared" si="4"/>
+      <c r="V34" s="35">
+        <f>VLOOKUP(O34,tag,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="V27" s="34">
-        <f t="shared" si="5"/>
+      <c r="W34" s="35">
+        <f>VLOOKUP(O34,tag,7,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="X34" s="36">
+        <f>VLOOKUP(O34,tag,5,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="Y34" s="36">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="14:25" x14ac:dyDescent="0.3">
+      <c r="N35" s="32"/>
+      <c r="O35" s="33" t="s">
+        <v>648</v>
+      </c>
+      <c r="P35" s="34">
+        <v>57</v>
+      </c>
+      <c r="Q35" s="35">
+        <f>VLOOKUP(O35,tag,9,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="W27" s="34">
-        <f t="shared" si="6"/>
+      <c r="R35" s="35">
+        <f>VLOOKUP(O35,tag,8,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="S35" s="36">
+        <f>VLOOKUP(O35,tag,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="T35" s="35">
+        <f>VLOOKUP(O35,tag,10,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="X27" s="35">
-        <f t="shared" si="7"/>
+      <c r="U35" s="35">
+        <f>VLOOKUP(O35,tag,3,FALSE)+VLOOKUP(O35,tag,4,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="V35" s="35">
+        <f>VLOOKUP(O35,tag,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="W35" s="35">
+        <f>VLOOKUP(O35,tag,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="X35" s="36">
+        <f>VLOOKUP(O35,tag,5,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="Y27" s="35">
-        <f t="shared" si="8"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="N28" s="45"/>
-      <c r="O28" s="32" t="s">
-        <v>208</v>
-      </c>
-      <c r="P28" s="33">
-        <v>55</v>
-      </c>
-      <c r="Q28" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R28" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S28" s="35">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="T28" s="34">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="U28" s="34">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="V28" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W28" s="34">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="X28" s="35">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="Y28" s="35">
-        <f t="shared" si="8"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="N29" s="45"/>
-      <c r="O29" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="P29" s="33">
-        <v>51</v>
-      </c>
-      <c r="Q29" s="34">
+      <c r="Y35" s="36">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="R29" s="34">
-        <f t="shared" si="1"/>
+    </row>
+    <row r="36" spans="14:25" x14ac:dyDescent="0.3">
+      <c r="N36" s="37" t="s">
+        <v>840</v>
+      </c>
+      <c r="O36" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="P36" s="34">
+        <v>10</v>
+      </c>
+      <c r="Q36" s="35">
+        <f>VLOOKUP(O36,tag,9,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="S29" s="35">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="T29" s="34">
-        <f t="shared" si="3"/>
+      <c r="R36" s="35">
+        <f>VLOOKUP(O36,tag,8,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="U29" s="34">
-        <f t="shared" si="4"/>
+      <c r="S36" s="36">
+        <f>VLOOKUP(O36,tag,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="T36" s="35">
+        <f>VLOOKUP(O36,tag,10,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="V29" s="34">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="W29" s="34">
-        <f t="shared" si="6"/>
+      <c r="U36" s="35">
+        <f>VLOOKUP(O36,tag,3,FALSE)+VLOOKUP(O36,tag,4,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="X29" s="35">
-        <f t="shared" si="7"/>
-        <v>9</v>
-      </c>
-      <c r="Y29" s="35">
-        <f t="shared" si="8"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="N30" s="45" t="s">
-        <v>839</v>
-      </c>
-      <c r="O30" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="P30" s="33">
-        <v>78</v>
-      </c>
-      <c r="Q30" s="34">
+      <c r="V36" s="35">
+        <f>VLOOKUP(O36,tag,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="W36" s="35">
+        <f>VLOOKUP(O36,tag,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="X36" s="36">
+        <f>VLOOKUP(O36,tag,5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="Y36" s="36">
         <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="14:25" x14ac:dyDescent="0.3">
+      <c r="N37" s="37"/>
+      <c r="O37" s="33" t="s">
+        <v>244</v>
+      </c>
+      <c r="P37" s="34">
+        <v>19</v>
+      </c>
+      <c r="Q37" s="35">
+        <f>VLOOKUP(O37,tag,9,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="R30" s="34">
-        <f t="shared" si="1"/>
+      <c r="R37" s="35">
+        <f>VLOOKUP(O37,tag,8,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="S30" s="35">
-        <f t="shared" si="2"/>
-        <v>16</v>
-      </c>
-      <c r="T30" s="34">
-        <f t="shared" si="3"/>
+      <c r="S37" s="36">
+        <f>VLOOKUP(O37,tag,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="T37" s="35">
+        <f>VLOOKUP(O37,tag,10,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="U30" s="34">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="V30" s="34">
-        <f t="shared" si="5"/>
+      <c r="U37" s="35">
+        <f>VLOOKUP(O37,tag,3,FALSE)+VLOOKUP(O37,tag,4,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="W30" s="34">
-        <f t="shared" si="6"/>
+      <c r="V37" s="35">
+        <f>VLOOKUP(O37,tag,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="X30" s="35">
-        <f t="shared" si="7"/>
+      <c r="W37" s="35">
+        <f>VLOOKUP(O37,tag,7,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="Y30" s="35">
-        <f t="shared" si="8"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="N31" s="45"/>
-      <c r="O31" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="P31" s="33">
-        <v>51</v>
-      </c>
-      <c r="Q31" s="34">
+      <c r="X37" s="36">
+        <f>VLOOKUP(O37,tag,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="36">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="R31" s="34">
-        <f t="shared" si="1"/>
+    </row>
+    <row r="38" spans="14:25" x14ac:dyDescent="0.3">
+      <c r="N38" s="37"/>
+      <c r="O38" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="P38" s="34">
+        <v>41</v>
+      </c>
+      <c r="Q38" s="35">
+        <f>VLOOKUP(O38,tag,9,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="S31" s="35">
-        <f t="shared" si="2"/>
-        <v>16</v>
-      </c>
-      <c r="T31" s="34">
-        <f t="shared" si="3"/>
+      <c r="R38" s="35">
+        <f>VLOOKUP(O38,tag,8,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="U31" s="34">
-        <f t="shared" si="4"/>
+      <c r="S38" s="36">
+        <f>VLOOKUP(O38,tag,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="T38" s="35">
+        <f>VLOOKUP(O38,tag,10,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="V31" s="34">
-        <f t="shared" si="5"/>
+      <c r="U38" s="35">
+        <f>VLOOKUP(O38,tag,3,FALSE)+VLOOKUP(O38,tag,4,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="W31" s="34">
-        <f t="shared" si="6"/>
+      <c r="V38" s="35">
+        <f>VLOOKUP(O38,tag,6,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="X31" s="35">
-        <f t="shared" si="7"/>
+      <c r="W38" s="35">
+        <f>VLOOKUP(O38,tag,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="X38" s="36">
+        <f>VLOOKUP(O38,tag,5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="Y38" s="36">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="Y31" s="35">
-        <f t="shared" si="8"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="N32" s="45"/>
-      <c r="O32" s="32" t="s">
-        <v>465</v>
-      </c>
-      <c r="P32" s="33">
-        <v>18</v>
-      </c>
-      <c r="Q32" s="34">
-        <f t="shared" si="0"/>
+    </row>
+    <row r="39" spans="14:25" x14ac:dyDescent="0.3">
+      <c r="N39" s="37"/>
+      <c r="O39" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="P39" s="34">
+        <v>19</v>
+      </c>
+      <c r="Q39" s="35">
+        <f>VLOOKUP(O39,tag,9,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="R32" s="34">
-        <f t="shared" si="1"/>
+      <c r="R39" s="35">
+        <f>VLOOKUP(O39,tag,8,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="S32" s="35">
-        <f t="shared" si="2"/>
+      <c r="S39" s="36">
+        <f>VLOOKUP(O39,tag,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="T39" s="35">
+        <f>VLOOKUP(O39,tag,10,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="U39" s="35">
+        <f>VLOOKUP(O39,tag,3,FALSE)+VLOOKUP(O39,tag,4,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="35">
+        <f>VLOOKUP(O39,tag,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="W39" s="35">
+        <f>VLOOKUP(O39,tag,7,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="T32" s="34">
-        <f t="shared" si="3"/>
+      <c r="X39" s="36">
+        <f>VLOOKUP(O39,tag,5,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="U32" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V32" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W32" s="34">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="X32" s="35">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="35">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="14:25" x14ac:dyDescent="0.3">
-      <c r="N33" s="45"/>
-      <c r="O33" s="32" t="s">
-        <v>116</v>
-      </c>
-      <c r="P33" s="33">
-        <v>90</v>
-      </c>
-      <c r="Q33" s="34">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="R33" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S33" s="35">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="T33" s="34">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="U33" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V33" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W33" s="34">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="X33" s="35">
-        <f t="shared" si="7"/>
-        <v>5</v>
-      </c>
-      <c r="Y33" s="35">
-        <f t="shared" si="8"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="14:25" x14ac:dyDescent="0.3">
-      <c r="N34" s="45"/>
-      <c r="O34" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="P34" s="33">
-        <v>65</v>
-      </c>
-      <c r="Q34" s="34">
+      <c r="Y39" s="36">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="R34" s="34">
-        <f t="shared" si="1"/>
+    </row>
+    <row r="40" spans="14:25" x14ac:dyDescent="0.3">
+      <c r="N40" s="37"/>
+      <c r="O40" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="P40" s="39">
+        <v>10</v>
+      </c>
+      <c r="Q40" s="35">
+        <f>VLOOKUP(O40,tag,9,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="R40" s="35">
+        <f>VLOOKUP(O40,tag,8,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="S34" s="35">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="T34" s="34">
-        <f t="shared" si="3"/>
+      <c r="S40" s="36">
+        <f>VLOOKUP(O40,tag,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="T40" s="35">
+        <f>VLOOKUP(O40,tag,10,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="U40" s="35">
+        <f>VLOOKUP(O40,tag,3,FALSE)+VLOOKUP(O40,tag,4,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="35">
+        <f>VLOOKUP(O40,tag,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="W40" s="35">
+        <f>VLOOKUP(O40,tag,7,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="X40" s="36">
+        <f>VLOOKUP(O40,tag,5,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="U34" s="34">
-        <f t="shared" si="4"/>
+      <c r="Y40" s="36">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="14:25" x14ac:dyDescent="0.3">
+      <c r="N41" s="37"/>
+      <c r="O41" s="33" t="s">
+        <v>836</v>
+      </c>
+      <c r="P41" s="34">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="35">
         <v>0</v>
       </c>
-      <c r="V34" s="34">
-        <f t="shared" si="5"/>
+      <c r="R41" s="35">
         <v>0</v>
       </c>
-      <c r="W34" s="34">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="X34" s="35">
-        <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="Y34" s="35">
-        <f t="shared" si="8"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="14:25" x14ac:dyDescent="0.3">
-      <c r="N35" s="45"/>
-      <c r="O35" s="32" t="s">
-        <v>648</v>
-      </c>
-      <c r="P35" s="33">
-        <v>57</v>
-      </c>
-      <c r="Q35" s="34">
-        <f t="shared" si="0"/>
+      <c r="S41" s="36">
         <v>0</v>
       </c>
-      <c r="R35" s="34">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="S35" s="35">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="T35" s="34">
-        <f t="shared" si="3"/>
+      <c r="T41" s="35">
         <v>0</v>
       </c>
-      <c r="U35" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V35" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W35" s="34">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="X35" s="35">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="Y35" s="35">
-        <f t="shared" si="8"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="14:25" x14ac:dyDescent="0.3">
-      <c r="N36" s="46" t="s">
-        <v>840</v>
-      </c>
-      <c r="O36" s="32" t="s">
-        <v>203</v>
-      </c>
-      <c r="P36" s="33">
-        <v>10</v>
-      </c>
-      <c r="Q36" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R36" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S36" s="35">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="T36" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U36" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V36" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W36" s="34">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="X36" s="35">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="Y36" s="35">
-        <f t="shared" si="8"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="14:25" x14ac:dyDescent="0.3">
-      <c r="N37" s="46"/>
-      <c r="O37" s="32" t="s">
-        <v>244</v>
-      </c>
-      <c r="P37" s="33">
-        <v>19</v>
-      </c>
-      <c r="Q37" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R37" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S37" s="35">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="T37" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U37" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V37" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W37" s="34">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="X37" s="35">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="Y37" s="35">
-        <f t="shared" si="8"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="14:25" x14ac:dyDescent="0.3">
-      <c r="N38" s="46"/>
-      <c r="O38" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="P38" s="33">
-        <v>41</v>
-      </c>
-      <c r="Q38" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R38" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S38" s="35">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="T38" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U38" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V38" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W38" s="34">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="X38" s="35">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="Y38" s="35">
-        <f t="shared" si="8"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="14:25" x14ac:dyDescent="0.3">
-      <c r="N39" s="46"/>
-      <c r="O39" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="P39" s="33">
-        <v>19</v>
-      </c>
-      <c r="Q39" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R39" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S39" s="35">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="T39" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U39" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V39" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W39" s="34">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="X39" s="35">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="Y39" s="35">
-        <f t="shared" si="8"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="14:25" x14ac:dyDescent="0.3">
-      <c r="N40" s="46"/>
-      <c r="O40" s="36" t="s">
-        <v>198</v>
-      </c>
-      <c r="P40" s="37">
-        <v>10</v>
-      </c>
-      <c r="Q40" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R40" s="34">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="S40" s="35">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="T40" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U40" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V40" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W40" s="34">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="X40" s="35">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="Y40" s="35">
-        <f t="shared" si="8"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="14:25" x14ac:dyDescent="0.3">
-      <c r="N41" s="46"/>
-      <c r="O41" s="32" t="s">
-        <v>836</v>
-      </c>
-      <c r="P41" s="33">
-        <v>1</v>
-      </c>
-      <c r="Q41" s="34">
-        <v>0</v>
-      </c>
-      <c r="R41" s="34">
-        <v>0</v>
-      </c>
-      <c r="S41" s="35">
-        <v>0</v>
-      </c>
-      <c r="T41" s="34">
-        <v>0</v>
-      </c>
-      <c r="U41" s="34">
+      <c r="U41" s="35">
         <f>VLOOKUP(O25,tag,9,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="V41" s="35">
+      <c r="V41" s="36">
         <v>0</v>
       </c>
-      <c r="W41" s="35">
+      <c r="W41" s="36">
         <v>0</v>
       </c>
-      <c r="X41" s="35">
+      <c r="X41" s="36">
         <v>0</v>
       </c>
-      <c r="Y41" s="35">
-        <f t="shared" si="8"/>
+      <c r="Y41" s="36">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -39024,43 +38798,43 @@
         <v>841</v>
       </c>
       <c r="O42" s="42"/>
-      <c r="P42" s="38">
+      <c r="P42" s="43">
         <f>SUM(P25:P41)</f>
         <v>640</v>
       </c>
-      <c r="Q42" s="39">
+      <c r="Q42" s="44">
         <f>SUM(Q25:Q41)</f>
         <v>14</v>
       </c>
-      <c r="R42" s="39">
-        <f t="shared" ref="R42:X42" si="9">SUM(R25:R41)</f>
+      <c r="R42" s="44">
+        <f t="shared" ref="R42:X42" si="1">SUM(R25:R41)</f>
         <v>4</v>
       </c>
-      <c r="S42" s="39">
-        <f t="shared" si="9"/>
+      <c r="S42" s="44">
+        <f t="shared" si="1"/>
         <v>87</v>
       </c>
-      <c r="T42" s="39">
-        <f t="shared" si="9"/>
+      <c r="T42" s="44">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="U42" s="39">
-        <f t="shared" si="9"/>
+      <c r="U42" s="44">
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="V42" s="39">
-        <f t="shared" si="9"/>
+      <c r="V42" s="44">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="W42" s="39">
-        <f t="shared" si="9"/>
+      <c r="W42" s="44">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="X42" s="39">
-        <f t="shared" si="9"/>
+      <c r="X42" s="44">
+        <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="Y42" s="38">
+      <c r="Y42" s="43">
         <f>SUM(Y25:Y41)</f>
         <v>161</v>
       </c>
@@ -39149,7 +38923,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="132" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>19</v>
       </c>
@@ -39397,7 +39171,7 @@
         <v>46044.670740740738</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="264" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>40</v>
       </c>
@@ -39893,7 +39667,7 @@
         <v>46042.731064814812</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="231" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>76</v>
       </c>
@@ -40389,7 +40163,7 @@
         <v>46044.574837962966</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>109</v>
       </c>
@@ -42863,7 +42637,7 @@
         <v>46048.590254629627</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:20" ht="247.5" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>44</v>
       </c>
@@ -42925,7 +42699,7 @@
         <v>46048.592118055552</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="99" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:20" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>32</v>
       </c>
@@ -43473,7 +43247,7 @@
         <v>46048.552395833336</v>
       </c>
     </row>
-    <row r="72" spans="1:20" ht="66" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:20" ht="363" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>271</v>
       </c>
@@ -48935,7 +48709,7 @@
         <v>46048.600960648146</v>
       </c>
     </row>
-    <row r="161" spans="1:20" ht="33" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:20" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
         <v>510</v>
       </c>
@@ -49059,7 +48833,7 @@
         <v>46048.584270833337</v>
       </c>
     </row>
-    <row r="163" spans="1:20" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:20" ht="165" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
         <v>481</v>
       </c>
